--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P1412_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P1412_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5390826958703527</v>
+        <v>0.6501032187240511</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8594289369787165</v>
+        <v>0.9265176107012241</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5390833169035549</v>
+        <v>0.6501028809480247</v>
       </c>
       <c r="D2" t="n">
-        <v>0.859429343759079</v>
+        <v>0.9265175703355477</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4637793149407588</v>
+        <v>0.3492579342181188</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8347486533499999</v>
+        <v>0.8656566941240598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9990879506392875</v>
+        <v>0.9966501062587083</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9997996229467819</v>
+        <v>0.9995144489396723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8484004127966976</v>
+        <v>0.8942208462332302</v>
       </c>
     </row>
   </sheetData>
